--- a/nsns_courses/2025课程列表 - August27.xlsx
+++ b/nsns_courses/2025课程列表 - August27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qiang\source\Repo\nsns_courses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB76F79-1672-4F26-91DC-0C9025E420A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9857347-E320-4836-A476-FA97E618481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2D772B29-792D-42CE-9C63-F3F9E4697AEC}"/>
+    <workbookView xWindow="2880" yWindow="1176" windowWidth="18888" windowHeight="11160" xr2:uid="{2D772B29-792D-42CE-9C63-F3F9E4697AEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport Program" sheetId="5" r:id="rId1"/>
@@ -609,7 +609,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -642,19 +642,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="6"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,7 +746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -756,14 +774,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1411,7 +1436,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1434,7 +1459,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1454,7 +1479,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1477,7 +1502,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>102</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1500,7 +1525,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="17" t="s">
         <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1508,7 +1533,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>78</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1525,7 +1550,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1545,7 +1570,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1553,7 +1578,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1576,7 +1601,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1593,7 +1618,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1616,7 +1641,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1628,7 +1653,7 @@
       <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>107</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1648,7 +1673,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>79</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1668,7 +1693,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>87</v>
       </c>
       <c r="B16" s="14" t="s">
@@ -1685,7 +1710,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>88</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1702,7 +1727,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="21" t="s">
         <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1722,7 +1747,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>109</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1734,7 +1759,7 @@
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -1754,7 +1779,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>84</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1774,7 +1799,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1797,7 +1822,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1856,7 +1881,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="15" t="s">
         <v>104</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1943,7 +1968,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="23" t="s">
         <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1963,7 +1988,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="23" t="s">
         <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1983,7 +2008,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="23" t="s">
         <v>118</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2006,7 +2031,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="24" t="s">
         <v>119</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2023,7 +2048,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="23" t="s">
         <v>125</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2040,7 +2065,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="23" t="s">
         <v>125</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2053,7 +2078,7 @@
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="24" t="s">
         <v>121</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2124,7 +2149,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="25" t="s">
         <v>120</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2136,7 +2161,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="25" t="s">
         <v>116</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2153,7 +2178,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="25" t="s">
         <v>116</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2176,7 +2201,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="25" t="s">
         <v>113</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2199,7 +2224,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="25" t="s">
         <v>123</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2222,7 +2247,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="24" t="s">
         <v>110</v>
       </c>
       <c r="B7" s="1" t="s">
